--- a/daily_output/Shopee_upload_PH_2026-09-30.xlsx
+++ b/daily_output/Shopee_upload_PH_2026-09-30.xlsx
@@ -12980,7 +12980,7 @@
     <t xml:space="preserve">B0FQBZ5JC2</t>
   </si>
   <si>
-    <t xml:space="preserve">https://m.media-amazon.com/images/I/61y3C27eY5L._AC_SL1000_.jpg</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/jyankel0726switch-code/ai-management-shopee/claude/admiring-bardeen-8xil2p/framed-images/B0FQBZ5JC2_cover.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">https://m.media-amazon.com/images/I/61DglMaaQLL.jpg</t>
@@ -13017,7 +13017,7 @@
     <t xml:space="preserve">B0F9YJPV7R</t>
   </si>
   <si>
-    <t xml:space="preserve">https://m.media-amazon.com/images/I/61lT7Kwq-KL._AC_SL1000_.jpg</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/jyankel0726switch-code/ai-management-shopee/claude/admiring-bardeen-8xil2p/framed-images/B0F9YJPV7R_cover.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">https://m.media-amazon.com/images/I/51KoprlJVYL.jpg</t>
@@ -13054,7 +13054,7 @@
     <t xml:space="preserve">B0DYNZ24Z7</t>
   </si>
   <si>
-    <t xml:space="preserve">https://m.media-amazon.com/images/I/61gOSOWrAnL._AC_SL1000_.jpg</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/jyankel0726switch-code/ai-management-shopee/claude/admiring-bardeen-8xil2p/framed-images/B0DYNZ24Z7_cover.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">https://m.media-amazon.com/images/I/51oOtfmEluL.jpg</t>
